--- a/docs/StructureDefinition-Location-twltc.xlsx
+++ b/docs/StructureDefinition-Location-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location-twltc.xlsx
+++ b/docs/StructureDefinition-Location-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location-twltc.xlsx
+++ b/docs/StructureDefinition-Location-twltc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location-twltc.xlsx
+++ b/docs/StructureDefinition-Location-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location-twltc.xlsx
+++ b/docs/StructureDefinition-Location-twltc.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4113" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4111" uniqueCount="605">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -613,9 +613,6 @@
     <t>指明此地點執行的功能類型</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -623,721 +620,721 @@
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>Location.type.id</t>
+  </si>
+  <si>
+    <t>唯一可識別ID，以供資料項目間相互參照。</t>
+  </si>
+  <si>
+    <t>resource中資料項目的唯一ID（用於內部參照）。這可以是任何不含空格的字串。</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Location.type.extension</t>
+  </si>
+  <si>
+    <t>擴充的資料項目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Location.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/Coding-tw}
+</t>
+  </si>
+  <si>
+    <t>由專門術語系統（terminology system）定義的代碼</t>
+  </si>
+  <si>
+    <t>由專門術語系統（terminology system）所定義之代碼的參照</t>
+  </si>
+  <si>
+    <t>代碼可以在列舉清單（enumerations）或代碼清單（code lists）中非常隨意地定義，直至有非常正式的定義，例如：SNOMED CT—更多資訊見HL7 v3核心原則（Core Principles ）。編碼的排序是未定義的因而 **必須沒有（SHALL NOT）** 被用來推斷意義。一般來說，最多只有一個編碼值（coding values）會被標記為UserSelected = true。</t>
+  </si>
+  <si>
+    <t>允許代碼系統中的替代編碼，以及翻譯到其他編碼系統。</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Location.type.coding.id</t>
+  </si>
+  <si>
+    <t>resource中資料項目的唯一ID（用於內部參照），這可以是任何不含空格的字串。</t>
+  </si>
+  <si>
+    <t>Location.type.coding.extension</t>
+  </si>
+  <si>
+    <t>可用於表示不屬於此資料項目基本定義的附加資訊。為了擴充的使用安全和可管理，對擴充的定義和使用有一套嚴格的管理。儘管任何實作者都可以定義一個擴充，但作為擴充定義的一部分，有一套要求 **必須（SHALL）** 滿足。</t>
+  </si>
+  <si>
+    <t>無論使用或定義擴充的機構或管轄區，任何應用程式、專案或標準使用擴充都不背負任何污名（stigma）。使用擴充是允許FHIR規範為每個人保留一個核心的簡易性。</t>
+  </si>
+  <si>
+    <t>Location.type.coding.system</t>
+  </si>
+  <si>
+    <t>專門術語系統（terminology system）的識別</t>
+  </si>
+  <si>
+    <t>定義代碼中符號意義的代碼系統識別</t>
+  </si>
+  <si>
+    <t>URI可以是一個OID（urn:oid:...）或一個UUID（urn:uuid:...）；OID和UUID **必須（SHALL）** 參照HL7 OID註冊中心；否則，URI應該來自HL7的FHIR定義的特殊URI列表，或者它應該參照一些明確建立的系统定義。</t>
+  </si>
+  <si>
+    <t>需要明確說明符號定義的來源</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v3-RoleCode</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Location.type.coding.version</t>
+  </si>
+  <si>
+    <t>系統的版本—如果相關的話</t>
+  </si>
+  <si>
+    <t>選擇此代碼時使用的代碼系統版本；請注意，一個維護良好的代碼系統不需要版本報告，因為代碼的意義在不同系統版本中是一致的；然而，不能始終保證這點，當不能保證意義一致時， **必須（SHALL）** 將版本資訊也一併作交換。</t>
+  </si>
+  <si>
+    <t>如果專門術語沒有明確定義應該使用什麼字串來識別代碼系統的版本，建議使用版本正式發布的日期（用FHIR日期格式表示）作為版本日期。</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Location.type.coding.code</t>
+  </si>
+  <si>
+    <t>系統定義的語法之符號</t>
+  </si>
+  <si>
+    <t>系統定義的語法之符號；符號可能是一個預先定義的代碼，也可能是代碼系統定義的語法中的表達式（如後組合配對／後組合式）。</t>
+  </si>
+  <si>
+    <t>需要參照系統中的一個特定代碼</t>
+  </si>
+  <si>
+    <t>PTRES</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Location.type.coding.display</t>
+  </si>
+  <si>
+    <t>由系統定義的表示法</t>
+  </si>
+  <si>
+    <t>遵循系統的規則以呈現代碼含義的表示法</t>
+  </si>
+  <si>
+    <t>需要能為不了解此系統的讀者呈現可讀的代碼含義</t>
+  </si>
+  <si>
+    <t>Patient's Residence</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Location.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>此編碼是否由使用者直接選擇？</t>
+  </si>
+  <si>
+    <t>表明此編碼是由使用者直接選擇，例如：從可用項目（代碼或顯示名稱）的清單中選擇。</t>
+  </si>
+  <si>
+    <t>在一系列備選方案中，直接選擇的代碼是新翻譯最合適的起點；關於「直接選擇」的確切意義，存在模糊不清之處，可能需要貿易夥伴的同意，以更完整澄清此資料項目的使用及其後果。</t>
+  </si>
+  <si>
+    <t>已被確定為一個臨床安全準則—此確切的系統／代碼對(code pair)是被明確選擇的，而不是由系統根據一些規則或是程式語言處理判斷。</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Location.type.text</t>
+  </si>
+  <si>
+    <t>概念的文字表示法</t>
+  </si>
+  <si>
+    <t>輸入資料的使用者所見／所選／所說的人類可讀文字表述，和（或）其代表使用者的預期含義。</t>
+  </si>
+  <si>
+    <t>很多時候，此文字表述與其中一個代碼的顯示名稱相同。</t>
+  </si>
+  <si>
+    <t>專門術語中的代碼並不總是能捕捉人類使用的細微差別的正確意義，或者根本就沒有合適的代碼；這些情況下，文字表述被用來捕捉來源的全部意義。</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>Location.telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactPoint
+</t>
+  </si>
+  <si>
+    <t>位置相關的聯絡方式</t>
+  </si>
+  <si>
+    <t>此地點提供的通訊設備聯絡方式。這可能包括電話號碼、傳真號碼、手機號碼、電子郵件地址和網站。</t>
+  </si>
+  <si>
+    <t>.telecom</t>
+  </si>
+  <si>
+    <t>Location.telecom.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Location.telecom.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Location.telecom.system</t>
+  </si>
+  <si>
+    <t>phone | fax | email | pager | url | sms | other</t>
+  </si>
+  <si>
+    <t>聯絡方式的通訊形式－需要什麼通訊系統進行聯絡</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.0.1</t>
+  </si>
+  <si>
+    <t>ContactPoint.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpt-2
+</t>
+  </si>
+  <si>
+    <t>./scheme</t>
+  </si>
+  <si>
+    <t>Location.telecom.value</t>
+  </si>
+  <si>
+    <t>實際的聯絡方式之細節</t>
+  </si>
+  <si>
+    <t>實際的聯絡方式之細節，針對指定的通訊系統提供有意義的形式（電話號碼或是電子郵件位址）</t>
+  </si>
+  <si>
+    <t>額外的文字資料，例如電話分機號碼、或關於聯絡人的說明，有時也包括於此值。</t>
+  </si>
+  <si>
+    <t>需支援非嚴格格式控制之舊有號碼</t>
+  </si>
+  <si>
+    <t>ContactPoint.value</t>
+  </si>
+  <si>
+    <t>./url</t>
+  </si>
+  <si>
+    <t>Location.telecom.use</t>
+  </si>
+  <si>
+    <t>home | work | temp | old | mobile</t>
+  </si>
+  <si>
+    <t>確定聯絡方式的用途</t>
+  </si>
+  <si>
+    <t>應用程式可以假定一個聯絡方法是目前使用中，除非它明確說它是暫時的或舊的。</t>
+  </si>
+  <si>
+    <t>需要追蹤此人使用這種聯絡的方式，使用者可以選擇適合他們用途的聯絡方式。</t>
+  </si>
+  <si>
+    <t>此聯絡方式的用途；應填入所綁定值集中的其中一個代碼。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.0.1</t>
+  </si>
+  <si>
+    <t>ContactPoint.use</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>Location.telecom.rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positiveInt
+</t>
+  </si>
+  <si>
+    <t>具體說明偏好的使用順序（1=最高優先順序）</t>
+  </si>
+  <si>
+    <t>具體說明使用一組聯繫方式的優先順序，較小排名序位的聯絡方式比較大排名序位的聯絡方式之序位還要前面。</t>
+  </si>
+  <si>
+    <t>請注意，排名序位沒有一定要遵循聯絡方式在實例中呈現的順序。</t>
+  </si>
+  <si>
+    <t>ContactPoint.rank</t>
+  </si>
+  <si>
+    <t>Location.telecom.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>此聯絡方式的使用效期</t>
+  </si>
+  <si>
+    <t>ContactPoint.period</t>
+  </si>
+  <si>
+    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
+  </si>
+  <si>
+    <t>Location.address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/Address-tw}
+</t>
+  </si>
+  <si>
+    <t>位置的地址資訊</t>
+  </si>
+  <si>
+    <t>實體地點</t>
+  </si>
+  <si>
+    <t>額外的地址應使用另一個Location resource 實例或透過 Organiztion 進行記錄</t>
+  </si>
+  <si>
+    <t>如果可以訪問地點，我們需要記錄其地址。</t>
+  </si>
+  <si>
+    <t>.addr</t>
+  </si>
+  <si>
+    <t>Location.address.id</t>
+  </si>
+  <si>
+    <t>Location.address.extension</t>
+  </si>
+  <si>
+    <t>Location.address.extension:room</t>
+  </si>
+  <si>
+    <t>room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-room}
+</t>
+  </si>
+  <si>
+    <t>室</t>
+  </si>
+  <si>
+    <t>臺灣地址欄位-室</t>
+  </si>
+  <si>
+    <t>Location.address.extension:floor</t>
+  </si>
+  <si>
+    <t>floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-floor}
+</t>
+  </si>
+  <si>
+    <t>樓</t>
+  </si>
+  <si>
+    <t>臺灣地址欄位-樓</t>
+  </si>
+  <si>
+    <t>Location.address.extension:number</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-number}
+</t>
+  </si>
+  <si>
+    <t>號</t>
+  </si>
+  <si>
+    <t>臺灣地址欄位-號</t>
+  </si>
+  <si>
+    <t>Location.address.extension:alley</t>
+  </si>
+  <si>
+    <t>alley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-alley}
+</t>
+  </si>
+  <si>
+    <t>弄</t>
+  </si>
+  <si>
+    <t>臺灣地址欄位-弄</t>
+  </si>
+  <si>
+    <t>Location.address.extension:lane</t>
+  </si>
+  <si>
+    <t>lane</t>
+  </si>
+  <si>
+    <t>巷
+衖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-lane}
+</t>
+  </si>
+  <si>
+    <t>巷/衖</t>
+  </si>
+  <si>
+    <t>臺灣地址欄位-巷</t>
+  </si>
+  <si>
+    <t>Location.address.extension:section</t>
+  </si>
+  <si>
+    <t>section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-section}
+</t>
+  </si>
+  <si>
+    <t>段</t>
+  </si>
+  <si>
+    <t>臺灣地址欄位-段</t>
+  </si>
+  <si>
+    <t>Location.address.extension:neighborhood</t>
+  </si>
+  <si>
+    <t>neighborhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-neighborhood}
+</t>
+  </si>
+  <si>
+    <t>鄰</t>
+  </si>
+  <si>
+    <t>臺灣地址欄位-鄰</t>
+  </si>
+  <si>
+    <t>Location.address.extension:village</t>
+  </si>
+  <si>
+    <t>village</t>
+  </si>
+  <si>
+    <t>村
+里</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-village}
+</t>
+  </si>
+  <si>
+    <t>村(里)</t>
+  </si>
+  <si>
+    <t>臺灣地址欄位-村(里)</t>
+  </si>
+  <si>
+    <t>Location.address.use</t>
+  </si>
+  <si>
+    <t>home ｜ work ｜ temp ｜ old ｜ billing － 此地址的用途</t>
+  </si>
+  <si>
+    <t>此地址的用途</t>
+  </si>
+  <si>
+    <t>應用程式可假定一個地址是目前使用中，除非它明確說它是暫時的或舊的。</t>
+  </si>
+  <si>
+    <t>允許從清單中挑選適當的地址用途</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>應填入AddressUse值集中的其中一個代碼</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/address-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Address.use</t>
+  </si>
+  <si>
+    <t>Location.address.type</t>
+  </si>
+  <si>
+    <t>postal ｜ physical ｜ both</t>
+  </si>
+  <si>
+    <t>區分實際地址（你可以拜訪的地址）和郵寄地址（如郵政信箱和轉遞地址），大多數地址都是這兩種。</t>
+  </si>
+  <si>
+    <t>地址的定義指出「地址旨在描述郵政地址，而不是實體位置」。但許多應用程式追蹤一個地址是否具有雙重目的，既是一個可以拜訪的地點，亦是一個有效的投遞目的地，郵政地址經常被用作實體位置的代表（亦可見[Location](http://hl7.org/fhir/R4/location.html#)resource）。</t>
+  </si>
+  <si>
+    <t>both</t>
+  </si>
+  <si>
+    <t>應填入AddressType值集中的其中一個代碼</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/address-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Address.type</t>
+  </si>
+  <si>
+    <t>Location.address.text</t>
+  </si>
+  <si>
+    <t>地址的文字表述</t>
+  </si>
+  <si>
+    <t>具體說明整個地址，因為它應該顯示在郵政標籤上，這可替代或與特定的部分一起提供。</t>
+  </si>
+  <si>
+    <t>可以同時提供文字表述和各部分的地址資料項目內容。更新地址的應用程式 **必須（SHALL）** 確保當文字表述和各部分的地址資料項目內容都存在時，文字表述不包括各部分的地址資料項目內容中沒有的內容，意即兩者內容會一致。</t>
+  </si>
+  <si>
+    <t>一個可呈現的、未編碼的形式。</t>
+  </si>
+  <si>
+    <t>137 Nowhere Street, Erewhon 9132</t>
+  </si>
+  <si>
+    <t>Address.text</t>
+  </si>
+  <si>
+    <t>./formatted</t>
+  </si>
+  <si>
+    <t>Location.address.line</t>
+  </si>
+  <si>
+    <t>路
+街</t>
+  </si>
+  <si>
+    <t>路/街</t>
+  </si>
+  <si>
+    <t>此部分包含門牌號碼、公寓號碼、街道名稱、街道方向、郵政信箱號碼、送貨提示以及類似的地址資訊。</t>
+  </si>
+  <si>
+    <t>137 Nowhere Street</t>
+  </si>
+  <si>
+    <t>Address.line</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = AL]</t>
+  </si>
+  <si>
+    <t>Location.address.city</t>
+  </si>
+  <si>
+    <t>Municpality
+鄉鎮市區</t>
+  </si>
+  <si>
+    <t>鄉/鎮/市/區，定義上與國際的等級一致。原文為：Name of city, town etc.。</t>
+  </si>
+  <si>
+    <t>市、鄉、鎮、村或其他社區或配送中心的名稱。</t>
+  </si>
+  <si>
+    <t>Erewhon</t>
+  </si>
+  <si>
+    <t>Address.city</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = CTY]</t>
+  </si>
+  <si>
+    <t>Location.address.district</t>
+  </si>
+  <si>
+    <t>County
+市</t>
+  </si>
+  <si>
+    <t>縣/市，定義上與國際的等級一致。原文為：District name (aka county)。</t>
+  </si>
+  <si>
+    <t>行政區域（縣）的名稱</t>
+  </si>
+  <si>
+    <t>區（district）有時被稱為縣（country），但在一些區域（regions），「縣（country）」被用來代替市（直轄市），所以縣名應該用市名來代替傳達。</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>Address.district</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = CNT | CPA]</t>
+  </si>
+  <si>
+    <t>Location.address.state</t>
+  </si>
+  <si>
+    <t>Province
+Territory</t>
+  </si>
+  <si>
+    <t>國家的子單位（縮寫也可以）。原文為：Sub-unit of country (abbreviations ok)。</t>
+  </si>
+  <si>
+    <t>一個國家的子單位，在聯邦組織的國家中擁有有限的主權。如果代碼被普遍使用，可使用代碼（例如：美國2個字母的州代碼）。</t>
+  </si>
+  <si>
+    <t>Address.state</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = STA]</t>
+  </si>
+  <si>
+    <t>Location.address.postalCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zip
+</t>
+  </si>
+  <si>
+    <t>郵遞區號</t>
+  </si>
+  <si>
+    <t>指定一個由郵政服務定義的區域之郵遞區號</t>
+  </si>
+  <si>
+    <t>9132</t>
+  </si>
+  <si>
+    <t>Address.postalCode</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = ZIP]</t>
+  </si>
+  <si>
+    <t>Location.address.postalCode.id</t>
+  </si>
+  <si>
+    <t>xml：id（或JSON格式）。</t>
+  </si>
+  <si>
+    <t>Location.address.postalCode.extension</t>
+  </si>
+  <si>
+    <t>Location.address.postalCode.extension:PostalCode</t>
+  </si>
+  <si>
+    <t>PostalCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-postal-code}
+</t>
+  </si>
+  <si>
+    <t>臺灣郵遞區號</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
-  </si>
-  <si>
-    <t>CD</t>
-  </si>
-  <si>
-    <t>Location.type.id</t>
-  </si>
-  <si>
-    <t>唯一可識別ID，以供資料項目間相互參照。</t>
-  </si>
-  <si>
-    <t>resource中資料項目的唯一ID（用於內部參照）。這可以是任何不含空格的字串。</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>Location.type.extension</t>
-  </si>
-  <si>
-    <t>擴充的資料項目</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Location.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/Coding-tw}
-</t>
-  </si>
-  <si>
-    <t>由專門術語系統（terminology system）定義的代碼</t>
-  </si>
-  <si>
-    <t>由專門術語系統（terminology system）所定義之代碼的參照</t>
-  </si>
-  <si>
-    <t>代碼可以在列舉清單（enumerations）或代碼清單（code lists）中非常隨意地定義，直至有非常正式的定義，例如：SNOMED CT—更多資訊見HL7 v3核心原則（Core Principles ）。編碼的排序是未定義的因而 **必須沒有（SHALL NOT）** 被用來推斷意義。一般來說，最多只有一個編碼值（coding values）會被標記為UserSelected = true。</t>
-  </si>
-  <si>
-    <t>允許代碼系統中的替代編碼，以及翻譯到其他編碼系統。</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>Location.type.coding.id</t>
-  </si>
-  <si>
-    <t>resource中資料項目的唯一ID（用於內部參照），這可以是任何不含空格的字串。</t>
-  </si>
-  <si>
-    <t>Location.type.coding.extension</t>
-  </si>
-  <si>
-    <t>可用於表示不屬於此資料項目基本定義的附加資訊。為了擴充的使用安全和可管理，對擴充的定義和使用有一套嚴格的管理。儘管任何實作者都可以定義一個擴充，但作為擴充定義的一部分，有一套要求 **必須（SHALL）** 滿足。</t>
-  </si>
-  <si>
-    <t>無論使用或定義擴充的機構或管轄區，任何應用程式、專案或標準使用擴充都不背負任何污名（stigma）。使用擴充是允許FHIR規範為每個人保留一個核心的簡易性。</t>
-  </si>
-  <si>
-    <t>Location.type.coding.system</t>
-  </si>
-  <si>
-    <t>專門術語系統（terminology system）的識別</t>
-  </si>
-  <si>
-    <t>定義代碼中符號意義的代碼系統識別</t>
-  </si>
-  <si>
-    <t>URI可以是一個OID（urn:oid:...）或一個UUID（urn:uuid:...）；OID和UUID **必須（SHALL）** 參照HL7 OID註冊中心；否則，URI應該來自HL7的FHIR定義的特殊URI列表，或者它應該參照一些明確建立的系统定義。</t>
-  </si>
-  <si>
-    <t>需要明確說明符號定義的來源</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-RoleCode</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Location.type.coding.version</t>
-  </si>
-  <si>
-    <t>系統的版本—如果相關的話</t>
-  </si>
-  <si>
-    <t>選擇此代碼時使用的代碼系統版本；請注意，一個維護良好的代碼系統不需要版本報告，因為代碼的意義在不同系統版本中是一致的；然而，不能始終保證這點，當不能保證意義一致時， **必須（SHALL）** 將版本資訊也一併作交換。</t>
-  </si>
-  <si>
-    <t>如果專門術語沒有明確定義應該使用什麼字串來識別代碼系統的版本，建議使用版本正式發布的日期（用FHIR日期格式表示）作為版本日期。</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Location.type.coding.code</t>
-  </si>
-  <si>
-    <t>系統定義的語法之符號</t>
-  </si>
-  <si>
-    <t>系統定義的語法之符號；符號可能是一個預先定義的代碼，也可能是代碼系統定義的語法中的表達式（如後組合配對／後組合式）。</t>
-  </si>
-  <si>
-    <t>需要參照系統中的一個特定代碼</t>
-  </si>
-  <si>
-    <t>PTRES</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Location.type.coding.display</t>
-  </si>
-  <si>
-    <t>由系統定義的表示法</t>
-  </si>
-  <si>
-    <t>遵循系統的規則以呈現代碼含義的表示法</t>
-  </si>
-  <si>
-    <t>需要能為不了解此系統的讀者呈現可讀的代碼含義</t>
-  </si>
-  <si>
-    <t>Patient's Residence</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Location.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>此編碼是否由使用者直接選擇？</t>
-  </si>
-  <si>
-    <t>表明此編碼是由使用者直接選擇，例如：從可用項目（代碼或顯示名稱）的清單中選擇。</t>
-  </si>
-  <si>
-    <t>在一系列備選方案中，直接選擇的代碼是新翻譯最合適的起點；關於「直接選擇」的確切意義，存在模糊不清之處，可能需要貿易夥伴的同意，以更完整澄清此資料項目的使用及其後果。</t>
-  </si>
-  <si>
-    <t>已被確定為一個臨床安全準則—此確切的系統／代碼對(code pair)是被明確選擇的，而不是由系統根據一些規則或是程式語言處理判斷。</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Location.type.text</t>
-  </si>
-  <si>
-    <t>概念的文字表示法</t>
-  </si>
-  <si>
-    <t>輸入資料的使用者所見／所選／所說的人類可讀文字表述，和（或）其代表使用者的預期含義。</t>
-  </si>
-  <si>
-    <t>很多時候，此文字表述與其中一個代碼的顯示名稱相同。</t>
-  </si>
-  <si>
-    <t>專門術語中的代碼並不總是能捕捉人類使用的細微差別的正確意義，或者根本就沒有合適的代碼；這些情況下，文字表述被用來捕捉來源的全部意義。</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Location.telecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ContactPoint
-</t>
-  </si>
-  <si>
-    <t>位置相關的聯絡方式</t>
-  </si>
-  <si>
-    <t>此地點提供的通訊設備聯絡方式。這可能包括電話號碼、傳真號碼、手機號碼、電子郵件地址和網站。</t>
-  </si>
-  <si>
-    <t>.telecom</t>
-  </si>
-  <si>
-    <t>Location.telecom.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Location.telecom.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Location.telecom.system</t>
-  </si>
-  <si>
-    <t>phone | fax | email | pager | url | sms | other</t>
-  </si>
-  <si>
-    <t>聯絡方式的通訊形式－需要什麼通訊系統進行聯絡</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.0.1</t>
-  </si>
-  <si>
-    <t>ContactPoint.system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpt-2
-</t>
-  </si>
-  <si>
-    <t>./scheme</t>
-  </si>
-  <si>
-    <t>Location.telecom.value</t>
-  </si>
-  <si>
-    <t>實際的聯絡方式之細節</t>
-  </si>
-  <si>
-    <t>實際的聯絡方式之細節，針對指定的通訊系統提供有意義的形式（電話號碼或是電子郵件位址）</t>
-  </si>
-  <si>
-    <t>額外的文字資料，例如電話分機號碼、或關於聯絡人的說明，有時也包括於此值。</t>
-  </si>
-  <si>
-    <t>需支援非嚴格格式控制之舊有號碼</t>
-  </si>
-  <si>
-    <t>ContactPoint.value</t>
-  </si>
-  <si>
-    <t>./url</t>
-  </si>
-  <si>
-    <t>Location.telecom.use</t>
-  </si>
-  <si>
-    <t>home | work | temp | old | mobile</t>
-  </si>
-  <si>
-    <t>確定聯絡方式的用途</t>
-  </si>
-  <si>
-    <t>應用程式可以假定一個聯絡方法是目前使用中，除非它明確說它是暫時的或舊的。</t>
-  </si>
-  <si>
-    <t>需要追蹤此人使用這種聯絡的方式，使用者可以選擇適合他們用途的聯絡方式。</t>
-  </si>
-  <si>
-    <t>此聯絡方式的用途；應填入所綁定值集中的其中一個代碼。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.0.1</t>
-  </si>
-  <si>
-    <t>ContactPoint.use</t>
-  </si>
-  <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
-    <t>Location.telecom.rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positiveInt
-</t>
-  </si>
-  <si>
-    <t>具體說明偏好的使用順序（1=最高優先順序）</t>
-  </si>
-  <si>
-    <t>具體說明使用一組聯繫方式的優先順序，較小排名序位的聯絡方式比較大排名序位的聯絡方式之序位還要前面。</t>
-  </si>
-  <si>
-    <t>請注意，排名序位沒有一定要遵循聯絡方式在實例中呈現的順序。</t>
-  </si>
-  <si>
-    <t>ContactPoint.rank</t>
-  </si>
-  <si>
-    <t>Location.telecom.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>此聯絡方式的使用效期</t>
-  </si>
-  <si>
-    <t>ContactPoint.period</t>
-  </si>
-  <si>
-    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
-  </si>
-  <si>
-    <t>Location.address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Address {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/Address-tw}
-</t>
-  </si>
-  <si>
-    <t>位置的地址資訊</t>
-  </si>
-  <si>
-    <t>實體地點</t>
-  </si>
-  <si>
-    <t>額外的地址應使用另一個Location resource 實例或透過 Organiztion 進行記錄</t>
-  </si>
-  <si>
-    <t>如果可以訪問地點，我們需要記錄其地址。</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>Location.address.id</t>
-  </si>
-  <si>
-    <t>Location.address.extension</t>
-  </si>
-  <si>
-    <t>Location.address.extension:room</t>
-  </si>
-  <si>
-    <t>room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-room}
-</t>
-  </si>
-  <si>
-    <t>室</t>
-  </si>
-  <si>
-    <t>臺灣地址欄位-室</t>
-  </si>
-  <si>
-    <t>Location.address.extension:floor</t>
-  </si>
-  <si>
-    <t>floor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-floor}
-</t>
-  </si>
-  <si>
-    <t>樓</t>
-  </si>
-  <si>
-    <t>臺灣地址欄位-樓</t>
-  </si>
-  <si>
-    <t>Location.address.extension:number</t>
-  </si>
-  <si>
-    <t>number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-number}
-</t>
-  </si>
-  <si>
-    <t>號</t>
-  </si>
-  <si>
-    <t>臺灣地址欄位-號</t>
-  </si>
-  <si>
-    <t>Location.address.extension:alley</t>
-  </si>
-  <si>
-    <t>alley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-alley}
-</t>
-  </si>
-  <si>
-    <t>弄</t>
-  </si>
-  <si>
-    <t>臺灣地址欄位-弄</t>
-  </si>
-  <si>
-    <t>Location.address.extension:lane</t>
-  </si>
-  <si>
-    <t>lane</t>
-  </si>
-  <si>
-    <t>巷
-衖</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-lane}
-</t>
-  </si>
-  <si>
-    <t>巷/衖</t>
-  </si>
-  <si>
-    <t>臺灣地址欄位-巷</t>
-  </si>
-  <si>
-    <t>Location.address.extension:section</t>
-  </si>
-  <si>
-    <t>section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-section}
-</t>
-  </si>
-  <si>
-    <t>段</t>
-  </si>
-  <si>
-    <t>臺灣地址欄位-段</t>
-  </si>
-  <si>
-    <t>Location.address.extension:neighborhood</t>
-  </si>
-  <si>
-    <t>neighborhood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-neighborhood}
-</t>
-  </si>
-  <si>
-    <t>鄰</t>
-  </si>
-  <si>
-    <t>臺灣地址欄位-鄰</t>
-  </si>
-  <si>
-    <t>Location.address.extension:village</t>
-  </si>
-  <si>
-    <t>village</t>
-  </si>
-  <si>
-    <t>村
-里</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-village}
-</t>
-  </si>
-  <si>
-    <t>村(里)</t>
-  </si>
-  <si>
-    <t>臺灣地址欄位-村(里)</t>
-  </si>
-  <si>
-    <t>Location.address.use</t>
-  </si>
-  <si>
-    <t>home ｜ work ｜ temp ｜ old ｜ billing － 此地址的用途</t>
-  </si>
-  <si>
-    <t>此地址的用途</t>
-  </si>
-  <si>
-    <t>應用程式可假定一個地址是目前使用中，除非它明確說它是暫時的或舊的。</t>
-  </si>
-  <si>
-    <t>允許從清單中挑選適當的地址用途</t>
-  </si>
-  <si>
-    <t>home</t>
-  </si>
-  <si>
-    <t>應填入AddressUse值集中的其中一個代碼</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/address-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Address.use</t>
-  </si>
-  <si>
-    <t>Location.address.type</t>
-  </si>
-  <si>
-    <t>postal ｜ physical ｜ both</t>
-  </si>
-  <si>
-    <t>區分實際地址（你可以拜訪的地址）和郵寄地址（如郵政信箱和轉遞地址），大多數地址都是這兩種。</t>
-  </si>
-  <si>
-    <t>地址的定義指出「地址旨在描述郵政地址，而不是實體位置」。但許多應用程式追蹤一個地址是否具有雙重目的，既是一個可以拜訪的地點，亦是一個有效的投遞目的地，郵政地址經常被用作實體位置的代表（亦可見[Location](http://hl7.org/fhir/R4/location.html#)resource）。</t>
-  </si>
-  <si>
-    <t>both</t>
-  </si>
-  <si>
-    <t>應填入AddressType值集中的其中一個代碼</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/address-type|4.0.1</t>
-  </si>
-  <si>
-    <t>Address.type</t>
-  </si>
-  <si>
-    <t>Location.address.text</t>
-  </si>
-  <si>
-    <t>地址的文字表述</t>
-  </si>
-  <si>
-    <t>具體說明整個地址，因為它應該顯示在郵政標籤上，這可替代或與特定的部分一起提供。</t>
-  </si>
-  <si>
-    <t>可以同時提供文字表述和各部分的地址資料項目內容。更新地址的應用程式 **必須（SHALL）** 確保當文字表述和各部分的地址資料項目內容都存在時，文字表述不包括各部分的地址資料項目內容中沒有的內容，意即兩者內容會一致。</t>
-  </si>
-  <si>
-    <t>一個可呈現的、未編碼的形式。</t>
-  </si>
-  <si>
-    <t>137 Nowhere Street, Erewhon 9132</t>
-  </si>
-  <si>
-    <t>Address.text</t>
-  </si>
-  <si>
-    <t>./formatted</t>
-  </si>
-  <si>
-    <t>Location.address.line</t>
-  </si>
-  <si>
-    <t>路
-街</t>
-  </si>
-  <si>
-    <t>路/街</t>
-  </si>
-  <si>
-    <t>此部分包含門牌號碼、公寓號碼、街道名稱、街道方向、郵政信箱號碼、送貨提示以及類似的地址資訊。</t>
-  </si>
-  <si>
-    <t>137 Nowhere Street</t>
-  </si>
-  <si>
-    <t>Address.line</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = AL]</t>
-  </si>
-  <si>
-    <t>Location.address.city</t>
-  </si>
-  <si>
-    <t>Municpality
-鄉鎮市區</t>
-  </si>
-  <si>
-    <t>鄉/鎮/市/區，定義上與國際的等級一致。原文為：Name of city, town etc.。</t>
-  </si>
-  <si>
-    <t>市、鄉、鎮、村或其他社區或配送中心的名稱。</t>
-  </si>
-  <si>
-    <t>Erewhon</t>
-  </si>
-  <si>
-    <t>Address.city</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = CTY]</t>
-  </si>
-  <si>
-    <t>Location.address.district</t>
-  </si>
-  <si>
-    <t>County
-市</t>
-  </si>
-  <si>
-    <t>縣/市，定義上與國際的等級一致。原文為：District name (aka county)。</t>
-  </si>
-  <si>
-    <t>行政區域（縣）的名稱</t>
-  </si>
-  <si>
-    <t>區（district）有時被稱為縣（country），但在一些區域（regions），「縣（country）」被用來代替市（直轄市），所以縣名應該用市名來代替傳達。</t>
-  </si>
-  <si>
-    <t>Madison</t>
-  </si>
-  <si>
-    <t>Address.district</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = CNT | CPA]</t>
-  </si>
-  <si>
-    <t>Location.address.state</t>
-  </si>
-  <si>
-    <t>Province
-Territory</t>
-  </si>
-  <si>
-    <t>國家的子單位（縮寫也可以）。原文為：Sub-unit of country (abbreviations ok)。</t>
-  </si>
-  <si>
-    <t>一個國家的子單位，在聯邦組織的國家中擁有有限的主權。如果代碼被普遍使用，可使用代碼（例如：美國2個字母的州代碼）。</t>
-  </si>
-  <si>
-    <t>Address.state</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = STA]</t>
-  </si>
-  <si>
-    <t>Location.address.postalCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zip
-</t>
-  </si>
-  <si>
-    <t>郵遞區號</t>
-  </si>
-  <si>
-    <t>指定一個由郵政服務定義的區域之郵遞區號</t>
-  </si>
-  <si>
-    <t>9132</t>
-  </si>
-  <si>
-    <t>Address.postalCode</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = ZIP]</t>
-  </si>
-  <si>
-    <t>Location.address.postalCode.id</t>
-  </si>
-  <si>
-    <t>xml：id（或JSON格式）。</t>
-  </si>
-  <si>
-    <t>Location.address.postalCode.extension</t>
-  </si>
-  <si>
-    <t>Location.address.postalCode.extension:PostalCode</t>
-  </si>
-  <si>
-    <t>PostalCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://twcore.mohw.gov.tw/ig/twcore/StructureDefinition/tw-postal-code}
-</t>
-  </si>
-  <si>
-    <t>臺灣郵遞區號</t>
   </si>
   <si>
     <t>Location.address.postalCode.extension:PostalCode.id</t>
@@ -1620,6 +1617,9 @@
     <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
   </si>
   <si>
+    <t>.playingEntity [classCode=PLC].code</t>
+  </si>
+  <si>
     <t>Location.position</t>
   </si>
   <si>
@@ -1884,7 +1884,7 @@
     <t>Location.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -4117,7 +4117,7 @@
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>189</v>
@@ -4128,9 +4128,7 @@
       <c r="M18" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="N18" t="s" s="2">
-        <v>192</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -4155,13 +4153,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Z18" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -4188,24 +4186,24 @@
         <v>76</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4231,10 +4229,10 @@
         <v>164</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4285,7 +4283,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -4308,10 +4306,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4337,10 +4335,10 @@
         <v>130</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4379,19 +4377,19 @@
         <v>20</v>
       </c>
       <c r="AB20" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE20" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AC20" t="s" s="2">
+      <c r="AF20" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -4414,10 +4412,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4437,22 +4435,22 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4501,7 +4499,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -4510,13 +4508,13 @@
         <v>76</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
@@ -4524,10 +4522,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4553,10 +4551,10 @@
         <v>164</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4607,7 +4605,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -4630,10 +4628,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4659,13 +4657,13 @@
         <v>130</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4703,19 +4701,19 @@
         <v>20</v>
       </c>
       <c r="AB23" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE23" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AC23" t="s" s="2">
+      <c r="AF23" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -4738,10 +4736,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4767,16 +4765,16 @@
         <v>97</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4786,7 +4784,7 @@
         <v>20</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>20</v>
@@ -4825,7 +4823,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -4840,7 +4838,7 @@
         <v>95</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>20</v>
@@ -4848,10 +4846,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4877,13 +4875,13 @@
         <v>164</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4933,7 +4931,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -4948,7 +4946,7 @@
         <v>95</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>20</v>
@@ -4956,10 +4954,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4985,14 +4983,14 @@
         <v>103</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5002,7 +5000,7 @@
         <v>20</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>20</v>
@@ -5041,7 +5039,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -5056,7 +5054,7 @@
         <v>95</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>20</v>
@@ -5064,10 +5062,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5093,14 +5091,14 @@
         <v>164</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5110,7 +5108,7 @@
         <v>20</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>20</v>
@@ -5149,7 +5147,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -5164,7 +5162,7 @@
         <v>95</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>20</v>
@@ -5172,10 +5170,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5198,19 +5196,19 @@
         <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5259,7 +5257,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -5274,7 +5272,7 @@
         <v>95</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
@@ -5282,10 +5280,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5311,16 +5309,16 @@
         <v>164</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5369,7 +5367,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -5384,7 +5382,7 @@
         <v>95</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>20</v>
@@ -5392,10 +5390,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5418,13 +5416,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5475,7 +5473,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -5490,7 +5488,7 @@
         <v>95</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>20</v>
@@ -5498,10 +5496,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5527,10 +5525,10 @@
         <v>164</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5581,7 +5579,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -5604,10 +5602,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5636,7 +5634,7 @@
         <v>131</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>133</v>
@@ -5677,19 +5675,19 @@
         <v>20</v>
       </c>
       <c r="AB32" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE32" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AC32" t="s" s="2">
+      <c r="AF32" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -5712,10 +5710,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5741,10 +5739,10 @@
         <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5774,43 +5772,43 @@
         <v>151</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Z33" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI33" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>20</v>
@@ -5818,10 +5816,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5847,16 +5845,16 @@
         <v>164</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5905,7 +5903,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -5920,7 +5918,7 @@
         <v>95</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>20</v>
@@ -5928,10 +5926,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5957,16 +5955,16 @@
         <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5994,28 +5992,28 @@
         <v>151</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -6030,7 +6028,7 @@
         <v>95</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
@@ -6038,10 +6036,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6064,16 +6062,16 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6123,7 +6121,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -6146,10 +6144,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6172,13 +6170,13 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6229,7 +6227,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
@@ -6244,7 +6242,7 @@
         <v>95</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -6252,10 +6250,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6278,19 +6276,19 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6339,7 +6337,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -6348,13 +6346,13 @@
         <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
@@ -6362,10 +6360,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6391,10 +6389,10 @@
         <v>164</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6445,7 +6443,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -6468,10 +6466,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6500,7 +6498,7 @@
         <v>131</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>133</v>
@@ -6541,19 +6539,19 @@
         <v>20</v>
       </c>
       <c r="AB40" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE40" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AC40" t="s" s="2">
+      <c r="AF40" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -6576,13 +6574,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B41" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C41" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>20</v>
@@ -6604,13 +6602,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6661,7 +6659,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6684,13 +6682,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>20</v>
@@ -6712,13 +6710,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6769,7 +6767,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
@@ -6792,13 +6790,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>20</v>
@@ -6820,13 +6818,13 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6877,7 +6875,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
@@ -6900,13 +6898,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>20</v>
@@ -6928,13 +6926,13 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6985,7 +6983,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -7008,16 +7006,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="D45" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="D45" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7036,13 +7034,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7093,7 +7091,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -7116,13 +7114,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>20</v>
@@ -7144,13 +7142,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7201,7 +7199,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -7224,13 +7222,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>20</v>
@@ -7252,13 +7250,13 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7309,7 +7307,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>75</v>
@@ -7332,16 +7330,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="D48" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="D48" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7360,13 +7358,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7417,7 +7415,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -7440,10 +7438,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7469,16 +7467,16 @@
         <v>103</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7491,7 +7489,7 @@
         <v>20</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>20</v>
@@ -7506,28 +7504,28 @@
         <v>151</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
@@ -7542,7 +7540,7 @@
         <v>95</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
@@ -7550,10 +7548,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7579,13 +7577,13 @@
         <v>103</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7599,7 +7597,7 @@
         <v>20</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>20</v>
@@ -7614,28 +7612,28 @@
         <v>151</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -7650,7 +7648,7 @@
         <v>95</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>20</v>
@@ -7658,10 +7656,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7687,16 +7685,16 @@
         <v>164</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7709,7 +7707,7 @@
         <v>20</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>20</v>
@@ -7745,7 +7743,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -7760,7 +7758,7 @@
         <v>95</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>20</v>
@@ -7768,14 +7766,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7797,10 +7795,10 @@
         <v>164</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7815,7 +7813,7 @@
         <v>20</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>20</v>
@@ -7851,7 +7849,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -7866,7 +7864,7 @@
         <v>95</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>20</v>
@@ -7874,14 +7872,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7903,10 +7901,10 @@
         <v>164</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7921,7 +7919,7 @@
         <v>20</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>20</v>
@@ -7957,7 +7955,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -7972,7 +7970,7 @@
         <v>95</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>20</v>
@@ -7980,14 +7978,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8009,13 +8007,13 @@
         <v>164</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8029,7 +8027,7 @@
         <v>20</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>20</v>
@@ -8065,7 +8063,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -8080,7 +8078,7 @@
         <v>95</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>20</v>
@@ -8088,14 +8086,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8117,10 +8115,10 @@
         <v>164</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8171,7 +8169,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
@@ -8186,7 +8184,7 @@
         <v>95</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>20</v>
@@ -8194,14 +8192,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8223,10 +8221,10 @@
         <v>164</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8241,7 +8239,7 @@
         <v>20</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>20</v>
@@ -8277,7 +8275,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -8292,7 +8290,7 @@
         <v>95</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>20</v>
@@ -8300,10 +8298,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8329,10 +8327,10 @@
         <v>164</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8383,7 +8381,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -8406,10 +8404,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8435,10 +8433,10 @@
         <v>130</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8477,17 +8475,17 @@
         <v>20</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
@@ -8510,13 +8508,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C59" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>20</v>
@@ -8538,13 +8536,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8595,7 +8593,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -8604,7 +8602,7 @@
         <v>76</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>196</v>
+        <v>424</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>135</v>
@@ -8618,10 +8616,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8647,10 +8645,10 @@
         <v>164</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8701,7 +8699,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -8724,10 +8722,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8753,10 +8751,10 @@
         <v>130</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8795,19 +8793,19 @@
         <v>20</v>
       </c>
       <c r="AB61" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE61" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AC61" t="s" s="2">
+      <c r="AF61" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -8830,10 +8828,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8859,13 +8857,13 @@
         <v>97</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8873,49 +8871,49 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -8938,10 +8936,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8967,13 +8965,13 @@
         <v>189</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9023,7 +9021,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -9032,13 +9030,13 @@
         <v>83</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>197</v>
+        <v>127</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>20</v>
@@ -9046,10 +9044,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9075,10 +9073,10 @@
         <v>164</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9129,7 +9127,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -9152,10 +9150,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9181,13 +9179,13 @@
         <v>130</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9225,19 +9223,19 @@
         <v>20</v>
       </c>
       <c r="AB65" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE65" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AC65" t="s" s="2">
+      <c r="AF65" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -9260,10 +9258,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9283,22 +9281,22 @@
         <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L66" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O66" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9335,17 +9333,17 @@
         <v>20</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
@@ -9354,13 +9352,13 @@
         <v>76</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>20</v>
@@ -9368,13 +9366,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C67" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>20</v>
@@ -9393,22 +9391,22 @@
         <v>20</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L67" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O67" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -9436,11 +9434,11 @@
         <v>151</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>456</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>20</v>
       </c>
@@ -9457,7 +9455,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
@@ -9466,13 +9464,13 @@
         <v>76</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>20</v>
@@ -9480,10 +9478,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9509,10 +9507,10 @@
         <v>164</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9563,7 +9561,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
@@ -9586,10 +9584,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9615,13 +9613,13 @@
         <v>130</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9659,19 +9657,19 @@
         <v>20</v>
       </c>
       <c r="AB69" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AC69" t="s" s="2">
+      <c r="AF69" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9694,10 +9692,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9723,16 +9721,16 @@
         <v>97</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -9742,7 +9740,7 @@
         <v>20</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>20</v>
@@ -9781,7 +9779,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -9796,7 +9794,7 @@
         <v>95</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>20</v>
@@ -9804,10 +9802,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9833,13 +9831,13 @@
         <v>164</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9889,7 +9887,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
@@ -9904,7 +9902,7 @@
         <v>95</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>20</v>
@@ -9912,10 +9910,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9941,14 +9939,14 @@
         <v>103</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -9997,7 +9995,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -10012,7 +10010,7 @@
         <v>95</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>20</v>
@@ -10020,10 +10018,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10049,14 +10047,14 @@
         <v>164</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -10105,7 +10103,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -10120,7 +10118,7 @@
         <v>95</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>20</v>
@@ -10128,10 +10126,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10154,19 +10152,19 @@
         <v>84</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -10215,7 +10213,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
@@ -10230,7 +10228,7 @@
         <v>95</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>20</v>
@@ -10238,13 +10236,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C75" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>20</v>
@@ -10263,22 +10261,22 @@
         <v>20</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L75" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O75" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -10306,10 +10304,10 @@
         <v>151</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>20</v>
@@ -10327,7 +10325,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
@@ -10336,13 +10334,13 @@
         <v>76</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>20</v>
@@ -10350,10 +10348,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10379,10 +10377,10 @@
         <v>164</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10433,7 +10431,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
@@ -10456,10 +10454,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10485,13 +10483,13 @@
         <v>130</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10529,19 +10527,19 @@
         <v>20</v>
       </c>
       <c r="AB77" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE77" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AC77" t="s" s="2">
+      <c r="AF77" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>
@@ -10564,10 +10562,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10593,16 +10591,16 @@
         <v>97</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -10612,7 +10610,7 @@
         <v>20</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>20</v>
@@ -10651,7 +10649,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
@@ -10666,7 +10664,7 @@
         <v>95</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>20</v>
@@ -10674,10 +10672,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10703,13 +10701,13 @@
         <v>164</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10759,7 +10757,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>75</v>
@@ -10774,7 +10772,7 @@
         <v>95</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>20</v>
@@ -10782,10 +10780,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10811,14 +10809,14 @@
         <v>103</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -10867,7 +10865,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>75</v>
@@ -10882,7 +10880,7 @@
         <v>95</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>20</v>
@@ -10890,10 +10888,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10919,14 +10917,14 @@
         <v>164</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
@@ -10975,7 +10973,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>75</v>
@@ -10990,7 +10988,7 @@
         <v>95</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>20</v>
@@ -10998,10 +10996,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11024,19 +11022,19 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -11085,7 +11083,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>75</v>
@@ -11100,7 +11098,7 @@
         <v>95</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>20</v>
@@ -11108,13 +11106,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C83" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>20</v>
@@ -11133,22 +11131,22 @@
         <v>20</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L83" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O83" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -11176,10 +11174,10 @@
         <v>151</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>20</v>
@@ -11197,7 +11195,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>75</v>
@@ -11206,13 +11204,13 @@
         <v>76</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>20</v>
@@ -11220,10 +11218,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11249,10 +11247,10 @@
         <v>164</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11303,7 +11301,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>75</v>
@@ -11326,10 +11324,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11355,13 +11353,13 @@
         <v>130</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11399,19 +11397,19 @@
         <v>20</v>
       </c>
       <c r="AB85" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE85" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AC85" t="s" s="2">
+      <c r="AF85" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>75</v>
@@ -11434,10 +11432,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11463,16 +11461,16 @@
         <v>97</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
@@ -11482,7 +11480,7 @@
         <v>20</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>20</v>
@@ -11521,7 +11519,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
@@ -11536,7 +11534,7 @@
         <v>95</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>20</v>
@@ -11544,10 +11542,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11573,13 +11571,13 @@
         <v>164</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N87" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11629,7 +11627,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>75</v>
@@ -11644,7 +11642,7 @@
         <v>95</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>20</v>
@@ -11652,10 +11650,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11681,14 +11679,14 @@
         <v>103</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -11737,7 +11735,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
@@ -11752,7 +11750,7 @@
         <v>95</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>20</v>
@@ -11760,10 +11758,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11789,14 +11787,14 @@
         <v>164</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -11845,7 +11843,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -11860,7 +11858,7 @@
         <v>95</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>20</v>
@@ -11868,10 +11866,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11894,19 +11892,19 @@
         <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -11955,7 +11953,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>75</v>
@@ -11970,7 +11968,7 @@
         <v>95</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>20</v>
@@ -11978,10 +11976,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12007,16 +12005,16 @@
         <v>164</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -12065,7 +12063,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>75</v>
@@ -12080,7 +12078,7 @@
         <v>95</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>20</v>
@@ -12088,10 +12086,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12117,10 +12115,10 @@
         <v>164</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12144,34 +12142,34 @@
         <v>20</v>
       </c>
       <c r="W92" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>75</v>
@@ -12194,10 +12192,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12223,13 +12221,13 @@
         <v>164</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12279,7 +12277,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>75</v>
@@ -12294,7 +12292,7 @@
         <v>95</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>20</v>
@@ -12302,10 +12300,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12328,17 +12326,17 @@
         <v>84</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -12351,43 +12349,43 @@
         <v>20</v>
       </c>
       <c r="T94" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
@@ -12402,7 +12400,7 @@
         <v>95</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>20</v>
@@ -12410,10 +12408,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12433,22 +12431,20 @@
         <v>20</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>189</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" s="2"/>
+      <c r="O95" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -12473,14 +12469,14 @@
         <v>20</v>
       </c>
       <c r="X95" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="Y95" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="Y95" t="s" s="2">
+      <c r="Z95" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="Z95" t="s" s="2">
-        <v>517</v>
-      </c>
       <c r="AA95" t="s" s="2">
         <v>20</v>
       </c>
@@ -12497,7 +12493,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>75</v>
@@ -12506,16 +12502,16 @@
         <v>83</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>197</v>
+        <v>517</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
     </row>
     <row r="96">
@@ -12657,10 +12653,10 @@
         <v>164</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -12711,7 +12707,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>75</v>
@@ -12766,7 +12762,7 @@
         <v>131</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>133</v>
@@ -12819,7 +12815,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>75</v>
@@ -13517,10 +13513,10 @@
         <v>164</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13571,7 +13567,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>75</v>
@@ -13626,7 +13622,7 @@
         <v>131</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>133</v>
@@ -13667,19 +13663,19 @@
         <v>20</v>
       </c>
       <c r="AB106" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE106" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AC106" t="s" s="2">
+      <c r="AF106" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -13871,7 +13867,7 @@
         <v>20</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y108" t="s" s="2">
         <v>566</v>
@@ -14271,10 +14267,10 @@
         <v>164</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14325,7 +14321,7 @@
         <v>20</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>75</v>
@@ -14380,7 +14376,7 @@
         <v>131</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>133</v>
@@ -14433,7 +14429,7 @@
         <v>20</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>75</v>
@@ -14628,7 +14624,7 @@
         <v>151</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Z115" t="s" s="2">
         <v>590</v>
@@ -14698,7 +14694,7 @@
         <v>20</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="L116" t="s" s="2">
         <v>592</v>

--- a/docs/StructureDefinition-Location-twltc.xlsx
+++ b/docs/StructureDefinition-Location-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location-twltc.xlsx
+++ b/docs/StructureDefinition-Location-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
